--- a/outputs/daily/predictions_2026-06-12.xlsx
+++ b/outputs/daily/predictions_2026-06-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE3"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,225 +479,260 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>has_market</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>market_p_home</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>market_p_draw</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>market_p_away</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>market_p_over25</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>market_lambda_home</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>market_lambda_away</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>ml_p_home</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ml_p_draw</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ml_p_away</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>ml_p_over25</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ml_p_btts_yes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>dc_p_home</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>dc_p_draw</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>dc_p_away</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dc_p_over25</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dc_p_under25</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dc_p_btts_yes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dc_p_btts_no</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>mc_p_home</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>mc_p_draw</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>mc_p_away</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>mc_p_over25</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>mc_p_btts_yes</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>mc_avg_home_goals</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>mc_avg_away_goals</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>mc_avg_total_goals</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>final_p_home</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>final_p_draw</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>final_p_away</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>pick</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>top_score_1</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>top_score_1_prob</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>top_score_2</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>top_score_2_prob</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>top_score_3</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>top_score_3_prob</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>top_score_4</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>top_score_4_prob</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>top_score_5</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>top_score_5_prob</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>top_score_6</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>top_score_6_prob</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>top_score_7</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>top_score_7_prob</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>top_score_8</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>top_score_8_prob</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>top_score_9</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>top_score_9_prob</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>top_score_10</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>top_score_10_prob</t>
         </is>
@@ -753,167 +788,188 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.888483195066821</v>
+        <v>1.729779118107939</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7344773283105702</v>
-      </c>
-      <c r="M2" t="n">
+        <v>0.8640531174118877</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4972144846796657</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2778551532033426</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2249303621169916</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.599930327868852</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9700696721311474</v>
+      </c>
+      <c r="T2" t="n">
         <v>0.5582819493341942</v>
       </c>
-      <c r="N2" t="n">
+      <c r="U2" t="n">
         <v>0.3324587766831252</v>
       </c>
-      <c r="O2" t="n">
+      <c r="V2" t="n">
         <v>0.1092592739826807</v>
       </c>
-      <c r="P2" t="n">
+      <c r="W2" t="n">
         <v>0.4624211232462194</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="X2" t="n">
         <v>0.3542608554359882</v>
       </c>
-      <c r="R2" t="n">
-        <v>0.6375792880390909</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.2341947551667954</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.1282259567941137</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.4873166425818261</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.5126833574181739</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.451598289361143</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.548401710638857</v>
-      </c>
       <c r="Y2" t="n">
-        <v>0.6399049999999999</v>
+        <v>0.5676165731955537</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.23168</v>
+        <v>0.258126210821722</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.128415</v>
+        <v>0.1742572159827241</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.487495</v>
+        <v>0.4800198214219354</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.449815</v>
+        <v>0.5199801785780646</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.889805</v>
+        <v>0.487128663272914</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.73197</v>
+        <v>0.512871336727086</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.621775</v>
+        <v>0.56853</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5939657517513978</v>
+        <v>0.25636</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2882399670007768</v>
+        <v>0.17511</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1177942812478255</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
+        <v>0.4803</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.486245</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.730025</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.8645</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2.594525</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.5361886194377227</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.2920341858258614</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.1717771947364159</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="AK2" t="n">
-        <v>0.5939657517513978</v>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AR2" t="n">
+        <v>0.5361886194377227</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.1228676873517065</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.1181022368576255</v>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>0.1294377917751458</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.1270129167576302</v>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.1107513544278815</v>
-      </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AX2" t="n">
+        <v>0.111806026098679</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="AS2" t="n">
-        <v>0.09506912348542897</v>
-      </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>0.09660634539599851</v>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="AU2" t="n">
-        <v>0.08265630682362626</v>
-      </c>
-      <c r="AV2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>0.08590304631414739</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>3-0</t>
         </is>
       </c>
-      <c r="AW2" t="n">
-        <v>0.08148036485797373</v>
-      </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BD2" t="n">
+        <v>0.06446657640804207</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>0.05984548069065503</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BF2" t="n">
+        <v>0.05570254631424041</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>0.04324593673703131</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>4-0</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.03846857494054914</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="n">
+        <v>0.05340371354135885</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="BE2" t="n">
-        <v>0.03697470859407612</v>
+      <c r="BJ2" t="n">
+        <v>0.0482564583115596</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.04173650695059104</v>
       </c>
     </row>
     <row r="3">
@@ -966,167 +1022,188 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.630401482253932</v>
+        <v>1.710020340927313</v>
       </c>
       <c r="L3" t="n">
-        <v>1.004838341374228</v>
-      </c>
-      <c r="M3" t="n">
+        <v>0.944337579705359</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5597905149839977</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.25720104742508</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1830084375909223</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.775163043478261</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8948369565217392</v>
+      </c>
+      <c r="T3" t="n">
         <v>0.595624081293214</v>
       </c>
-      <c r="N3" t="n">
+      <c r="U3" t="n">
         <v>0.1883233378200571</v>
       </c>
-      <c r="O3" t="n">
+      <c r="V3" t="n">
         <v>0.2160525808867289</v>
       </c>
-      <c r="P3" t="n">
+      <c r="W3" t="n">
         <v>0.6060634664400587</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="X3" t="n">
         <v>0.494778992075029</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.5080699055919224</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.2704920055631597</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2214380888449179</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.4903801548009806</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.5096198451990195</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.5214937181730891</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.4785062818269109</v>
-      </c>
       <c r="Y3" t="n">
-        <v>0.509095</v>
+        <v>0.5426402346779358</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.268945</v>
+        <v>0.2616311868654818</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.22196</v>
+        <v>0.1957285784565826</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.490185</v>
+        <v>0.495128532813275</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.520335</v>
+        <v>0.504871467186725</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.63134</v>
+        <v>0.5119039627265273</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.00387</v>
+        <v>0.4880960372734727</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.63521</v>
+        <v>0.544295</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5562247022276328</v>
+        <v>0.259415</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2252992383044533</v>
+        <v>0.19629</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.218476059467914</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
+        <v>0.49521</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.71074</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.942885</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2.653625</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.5680446931157079</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.2342013839234224</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.1977539229608697</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="AK3" t="n">
-        <v>0.5562247022276328</v>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AR3" t="n">
+        <v>0.5680446931157079</v>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>0.1292152784964821</v>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AT3" t="n">
+        <v>0.1249536872077475</v>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="AO3" t="n">
-        <v>0.1051559757499822</v>
-      </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AV3" t="n">
+        <v>0.1089304612559015</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.1028490771015984</v>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
-        <v>0.09576035526841768</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.09529926489215648</v>
-      </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AZ3" t="n">
+        <v>0.0971242485450533</v>
+      </c>
+      <c r="BA3" t="inlineStr">
         <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="AU3" t="n">
-        <v>0.08344870376053524</v>
-      </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BB3" t="n">
+        <v>0.08170355271852653</v>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.05862467129644493</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.05536148020310704</v>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="AW3" t="n">
-        <v>0.06030193483828406</v>
-      </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BH3" t="n">
+        <v>0.05506917615838143</v>
+      </c>
+      <c r="BI3" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>0.05901839369300634</v>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.05204260839026377</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.05179202091262734</v>
-      </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BJ3" t="n">
+        <v>0.05363566479682946</v>
+      </c>
+      <c r="BK3" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="BE3" t="n">
-        <v>0.04811183827866181</v>
+      <c r="BL3" t="n">
+        <v>0.0458590389008687</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-12.xlsx
+++ b/outputs/daily/predictions_2026-06-12.xlsx
@@ -788,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.729779118107939</v>
+        <v>1.720993610659393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8640531174118877</v>
+        <v>0.8431561350180945</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -815,73 +815,73 @@
         <v>0.9700696721311474</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5582819493341942</v>
+        <v>0.5374118349130377</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3324587766831252</v>
+        <v>0.3807860426049485</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1092592739826807</v>
+        <v>0.08180212248201384</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4624211232462194</v>
+        <v>0.4411969010139096</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3542608554359882</v>
+        <v>0.3519270225327025</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5676165731955537</v>
+        <v>0.5708497638209415</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.258126210821722</v>
+        <v>0.2587235832535633</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1742572159827241</v>
+        <v>0.1704266529254948</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4800198214219354</v>
+        <v>0.4725325725429497</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5199801785780646</v>
+        <v>0.5274674274570503</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.487128663272914</v>
+        <v>0.4789169523031284</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.512871336727086</v>
+        <v>0.5210830476968715</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.56853</v>
+        <v>0.57177</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.25636</v>
+        <v>0.2571</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.17511</v>
+        <v>0.17113</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4803</v>
+        <v>0.472405</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.486245</v>
+        <v>0.477805</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.730025</v>
+        <v>1.7214</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8645</v>
+        <v>0.84309</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.594525</v>
+        <v>2.56449</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.5361886194377227</v>
+        <v>0.5296923770466649</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2920341858258614</v>
+        <v>0.3090980720064599</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1717771947364159</v>
+        <v>0.1612095509468752</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.5361886194377227</v>
+        <v>0.5296923770466649</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.1228676873517065</v>
+        <v>0.1228810043740921</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>0.1181022368576255</v>
+        <v>0.1213192933177061</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0.111806026098679</v>
+        <v>0.1140074744792526</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>0.09660634539599851</v>
+        <v>0.09612610154510066</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="BB2" t="n">
-        <v>0.08590304631414739</v>
+        <v>0.08815576832167414</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.06446657640804207</v>
+        <v>0.06540204504873585</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>0.05570254631424041</v>
+        <v>0.05514413552557142</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>0.05340371354135885</v>
+        <v>0.05373917898044486</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0482564583115596</v>
+        <v>0.04709448759781865</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>0.04173650695059104</v>
+        <v>0.04052465612656198</v>
       </c>
     </row>
     <row r="3">
@@ -1022,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.710020340927313</v>
+        <v>1.70321239390786</v>
       </c>
       <c r="L3" t="n">
-        <v>0.944337579705359</v>
+        <v>0.8601481910895873</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -1049,73 +1049,73 @@
         <v>0.8948369565217392</v>
       </c>
       <c r="T3" t="n">
-        <v>0.595624081293214</v>
+        <v>0.6436832539287399</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1883233378200571</v>
+        <v>0.175853349599793</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2160525808867289</v>
+        <v>0.180463396471467</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6060634664400587</v>
+        <v>0.5588333546332035</v>
       </c>
       <c r="X3" t="n">
-        <v>0.494778992075029</v>
+        <v>0.4914431288643932</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5426402346779358</v>
+        <v>0.5621873527643972</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2616311868654818</v>
+        <v>0.2612161783726463</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1957285784565826</v>
+        <v>0.1765964688629566</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.495128532813275</v>
+        <v>0.472332933509397</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.504871467186725</v>
+        <v>0.527667066490603</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5119039627265273</v>
+        <v>0.4831354854675727</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4880960372734727</v>
+        <v>0.5168645145324273</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.544295</v>
+        <v>0.563205</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.259415</v>
+        <v>0.25998</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.19629</v>
+        <v>0.176815</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.49521</v>
+        <v>0.472085</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.5102</v>
+        <v>0.48164</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71074</v>
+        <v>1.703935</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.942885</v>
+        <v>0.85947</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.653625</v>
+        <v>2.563405</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.5680446931157079</v>
+        <v>0.5897521830597574</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2342013839234224</v>
+        <v>0.2297331359231211</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1977539229608697</v>
+        <v>0.1805146810171215</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.5680446931157079</v>
+        <v>0.5897521830597574</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.1249536872077475</v>
+        <v>0.1241601487643417</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>0.1089304612559015</v>
+        <v>0.1199376162507371</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>0.1028490771015984</v>
+        <v>0.1117519401654132</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0971242485450533</v>
+        <v>0.096123229184032</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="BB3" t="n">
-        <v>0.08170355271852653</v>
+        <v>0.08833281678608208</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
@@ -1171,23 +1171,23 @@
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.05862467129644493</v>
+        <v>0.06344576317766046</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.05498328746972331</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BF3" t="n">
-        <v>0.05536148020310704</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="BH3" t="n">
-        <v>0.05506917615838143</v>
+        <v>0.05457275842956299</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>0.05363566479682946</v>
+        <v>0.04854369425684663</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>0.0458590389008687</v>
+        <v>0.04134011085216748</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-12.xlsx
+++ b/outputs/daily/predictions_2026-06-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL3"/>
+  <dimension ref="A1:BW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,100 +639,155 @@
       </c>
       <c r="AS1" t="inlineStr">
         <is>
+          <t>has_value_data</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>best_value_market</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>best_value_odds</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>best_value_probability</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>best_value_edge</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>best_value_ev</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>best_edge_market</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>best_edge_odds</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>best_edge_probability</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>best_edge</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>best_edge_ev</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
           <t>top_score_1</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>top_score_1_prob</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>top_score_2</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>top_score_2_prob</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>top_score_3</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>top_score_3_prob</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>top_score_4</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>top_score_4_prob</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>top_score_5</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>top_score_5_prob</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>top_score_6</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>top_score_6_prob</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>top_score_7</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>top_score_7_prob</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>top_score_8</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>top_score_8_prob</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>top_score_9</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>top_score_9_prob</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>top_score_10</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>top_score_10_prob</t>
         </is>
@@ -741,12 +796,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WC2026-003</t>
+          <t>WC2026-002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T19:00:00+00:00</t>
+          <t>2026-06-12T02:00:00+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -756,132 +811,132 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BMO Field</t>
+          <t>Estadio Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.720993610659393</v>
+        <v>1.490175104958082</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8431561350180945</v>
+        <v>1.081452526580976</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4972144846796657</v>
+        <v>0.3624180426291843</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2778551532033426</v>
+        <v>0.3047159793381476</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2249303621169916</v>
+        <v>0.3328659780326681</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4272901541992036</v>
       </c>
       <c r="R2" t="n">
-        <v>1.599930327868852</v>
+        <v>1.228014660905759</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9700696721311474</v>
+        <v>1.161985339094241</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5374118349130377</v>
+        <v>0.6021160820980298</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3807860426049485</v>
+        <v>0.2495490326659355</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08180212248201384</v>
+        <v>0.1483348852360347</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4411969010139096</v>
+        <v>0.5052140846212879</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3519270225327025</v>
+        <v>0.5599628463344619</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5708497638209415</v>
+        <v>0.4537154237648564</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2587235832535633</v>
+        <v>0.2836304841235756</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1704266529254948</v>
+        <v>0.2626540921115679</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4725325725429497</v>
+        <v>0.4744243244704778</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5274674274570503</v>
+        <v>0.5255756755295222</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4789169523031284</v>
+        <v>0.5242892460520909</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5210830476968715</v>
+        <v>0.4757107539479091</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.57177</v>
+        <v>0.452725</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2571</v>
+        <v>0.28302</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.17113</v>
+        <v>0.264255</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.472405</v>
+        <v>0.47445</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.477805</v>
+        <v>0.52427</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7214</v>
+        <v>1.489395</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.84309</v>
+        <v>1.086045</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.56449</v>
+        <v>2.57544</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.5296923770466649</v>
+        <v>0.4691367017271982</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.3090980720064599</v>
+        <v>0.2801361741992303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1612095509468752</v>
+        <v>0.2507271240735714</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -889,98 +944,135 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.5296923770466649</v>
-      </c>
-      <c r="AS2" t="inlineStr">
+        <v>0.4691367017271982</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.759244525315124</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.4691367017271982</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.1067186590980139</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.294462875865166</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.759244525315124</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.4691367017271982</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.1067186590980139</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.294462875865166</v>
+      </c>
+      <c r="BD2" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="AT2" t="n">
-        <v>0.1228810043740921</v>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BE2" t="n">
+        <v>0.1354546732909617</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="AV2" t="n">
-        <v>0.1213192933177061</v>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BG2" t="n">
+        <v>0.1015518821004055</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.09175053726746429</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.08872517754608897</v>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>0.1140074744792526</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.09612610154510066</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.08815576832167414</v>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.06540204504873585</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BM2" t="n">
+        <v>0.08484009701057763</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.0703209336141388</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.06658536303077779</v>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.04961192517153062</v>
+      </c>
+      <c r="BT2" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BF2" t="n">
-        <v>0.05514413552557142</v>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.05373917898044486</v>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.04709448759781865</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.04052465612656198</v>
+      <c r="BU2" t="n">
+        <v>0.04557478883416799</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.04468291196734953</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WC2026-004</t>
+          <t>WC2026-003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-12T22:00:00+00:00</t>
+          <t>2026-06-12T19:00:00+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -990,132 +1082,132 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>BMO Field</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.70321239390786</v>
+        <v>1.707153500383766</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8601481910895873</v>
+        <v>0.7684943520063754</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5597905149839977</v>
+        <v>0.5257855450396701</v>
       </c>
       <c r="O3" t="n">
-        <v>0.25720104742508</v>
+        <v>0.2642411410948064</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1830084375909223</v>
+        <v>0.2099733138655235</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.4401024487075228</v>
       </c>
       <c r="R3" t="n">
-        <v>1.775163043478261</v>
+        <v>1.560382037253008</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8948369565217392</v>
+        <v>0.8796179627469922</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6436832539287399</v>
+        <v>0.7255353306240498</v>
       </c>
       <c r="U3" t="n">
-        <v>0.175853349599793</v>
+        <v>0.1935797145033666</v>
       </c>
       <c r="V3" t="n">
-        <v>0.180463396471467</v>
+        <v>0.08088495487258358</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5588333546332035</v>
+        <v>0.4554868720635546</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4914431288643932</v>
+        <v>0.4133217268355135</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5621873527643972</v>
+        <v>0.5869639595689801</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2612161783726463</v>
+        <v>0.2584463682988004</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1765964688629566</v>
+        <v>0.1545896721322197</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.472332933509397</v>
+        <v>0.4499240961149735</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.527667066490603</v>
+        <v>0.5500759038850265</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4831354854675727</v>
+        <v>0.4500507402421317</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5168645145324273</v>
+        <v>0.5499492597578683</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.563205</v>
+        <v>0.587715</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.25998</v>
+        <v>0.257275</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.176815</v>
+        <v>0.15501</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.472085</v>
+        <v>0.449755</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.48164</v>
+        <v>0.449165</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.703935</v>
+        <v>1.70783</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.85947</v>
+        <v>0.7682099999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.563405</v>
+        <v>2.47604</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.5897521830597574</v>
+        <v>0.6109925736265305</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2297331359231211</v>
+        <v>0.238060948588801</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1805146810171215</v>
+        <v>0.1509464777846686</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1123,87 +1215,124 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.5897521830597574</v>
-      </c>
-      <c r="AS3" t="inlineStr">
+        <v>0.6109925736265305</v>
+      </c>
+      <c r="AS3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.901916112822293</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.6109925736265305</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.08520702858686036</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.1620566205950595</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.901916112822293</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.6109925736265305</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.08520702858686036</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.1620566205950595</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.1325518323395183</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.1225619813220132</v>
+      </c>
+      <c r="BH3" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="AT3" t="n">
-        <v>0.1241601487643417</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.1199376162507371</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.1117519401654132</v>
-      </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BI3" t="n">
+        <v>0.1213798401081743</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.09514317330296665</v>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="AZ3" t="n">
-        <v>0.096123229184032</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.08833281678608208</v>
-      </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BM3" t="n">
+        <v>0.09418819041667802</v>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>3-0</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>0.06344576317766046</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BO3" t="n">
+        <v>0.06974403847594821</v>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BF3" t="n">
-        <v>0.05498328746972331</v>
-      </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BQ3" t="n">
+        <v>0.05360248570813517</v>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BH3" t="n">
-        <v>0.05457275842956299</v>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BS3" t="n">
+        <v>0.05359789965488153</v>
+      </c>
+      <c r="BT3" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="BJ3" t="n">
-        <v>0.04854369425684663</v>
-      </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BU3" t="n">
+        <v>0.04239987344116766</v>
+      </c>
+      <c r="BV3" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="BL3" t="n">
-        <v>0.04134011085216748</v>
+      <c r="BW3" t="n">
+        <v>0.03619154618045903</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-12.xlsx
+++ b/outputs/daily/predictions_2026-06-12.xlsx
@@ -843,31 +843,31 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.490175104958082</v>
+        <v>1.490283585198356</v>
       </c>
       <c r="L2" t="n">
-        <v>1.081452526580976</v>
+        <v>1.092344046340702</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3624180426291843</v>
+        <v>0.3560472142682399</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3047159793381476</v>
+        <v>0.308401348237844</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3328659780326681</v>
+        <v>0.335551437493916</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4272901541992036</v>
+        <v>0.4333415671715702</v>
       </c>
       <c r="R2" t="n">
-        <v>1.228014660905759</v>
+        <v>1.228211897706258</v>
       </c>
       <c r="S2" t="n">
-        <v>1.161985339094241</v>
+        <v>1.181788102293742</v>
       </c>
       <c r="T2" t="n">
         <v>0.6021160820980298</v>
@@ -885,58 +885,58 @@
         <v>0.5599628463344619</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4537154237648564</v>
+        <v>0.4512131781781549</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2836304841235756</v>
+        <v>0.2833206666038897</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2626540921115679</v>
+        <v>0.2654661552179555</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4744243244704778</v>
+        <v>0.4772002109359952</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5255756755295222</v>
+        <v>0.5227997890640048</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5242892460520909</v>
+        <v>0.5271399184012189</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4757107539479091</v>
+        <v>0.4728600815987811</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.452725</v>
+        <v>0.45028</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.28302</v>
+        <v>0.2827</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.264255</v>
+        <v>0.26702</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.47445</v>
+        <v>0.47714</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.52427</v>
+        <v>0.527205</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.489395</v>
+        <v>1.48947</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.086045</v>
+        <v>1.09705</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.57544</v>
+        <v>2.58652</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.4691367017271982</v>
+        <v>0.4659628089861452</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2801361741992303</v>
+        <v>0.2815328673791875</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2507271240735714</v>
+        <v>0.2525043236346675</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.4691367017271982</v>
+        <v>0.4659628089861452</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2.759244525315124</v>
+        <v>2.80861627314016</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4691367017271982</v>
+        <v>0.4659628089861452</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1067186590980139</v>
+        <v>0.1099155947179052</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.294462875865166</v>
+        <v>0.3087107279965873</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2.759244525315124</v>
+        <v>2.80861627314016</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.4691367017271982</v>
+        <v>0.4659628089861452</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1067186590980139</v>
+        <v>0.1099155947179052</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.294462875865166</v>
+        <v>0.3087107279965873</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.1354546732909617</v>
+        <v>0.1353319549559535</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.1015518821004055</v>
+        <v>0.1003255753551344</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>0.09175053726746429</v>
+        <v>0.09167408682893671</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0.08872517754608897</v>
+        <v>0.0878781052261851</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>0.08484009701057763</v>
+        <v>0.08392418774656241</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>0.0703209336141388</v>
+        <v>0.07025121502645797</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.06658536303077779</v>
+        <v>0.06719502512535629</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.04961192517153062</v>
+        <v>0.05006982147565478</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.04557478883416799</v>
+        <v>0.04554012892973772</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.04468291196734953</v>
+        <v>0.04508875075371153</v>
       </c>
     </row>
     <row r="3">
@@ -1114,31 +1114,31 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.707153500383766</v>
+        <v>1.722157141352893</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7684943520063754</v>
+        <v>0.7644907110372486</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5257855450396701</v>
+        <v>0.532007395651278</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2642411410948064</v>
+        <v>0.2648563657036375</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2099733138655235</v>
+        <v>0.2031362386450845</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4401024487075228</v>
+        <v>0.4460436550382903</v>
       </c>
       <c r="R3" t="n">
-        <v>1.560382037253008</v>
+        <v>1.587661384469602</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8796179627469922</v>
+        <v>0.8723386155303982</v>
       </c>
       <c r="T3" t="n">
         <v>0.7255353306240498</v>
@@ -1156,58 +1156,58 @@
         <v>0.4133217268355135</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5869639595689801</v>
+        <v>0.5916223289257996</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2584463682988004</v>
+        <v>0.2563971966150133</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1545896721322197</v>
+        <v>0.1519804744591876</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4499240961149735</v>
+        <v>0.4527561768691967</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5500759038850265</v>
+        <v>0.5472438231308032</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4500507402421317</v>
+        <v>0.4498892667997818</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5499492597578683</v>
+        <v>0.5501107332002182</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.587715</v>
+        <v>0.59251</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.257275</v>
+        <v>0.25501</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.15501</v>
+        <v>0.15248</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.449755</v>
+        <v>0.452445</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.449165</v>
+        <v>0.44887</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.70783</v>
+        <v>1.722655</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.7682099999999999</v>
+        <v>0.76415</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.47604</v>
+        <v>2.486805</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6109925736265305</v>
+        <v>0.6146459062103785</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.238060948588801</v>
+        <v>0.2377947455113866</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1509464777846686</v>
+        <v>0.147559348278235</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.6109925736265305</v>
+        <v>0.6146459062103785</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.901916112822293</v>
+        <v>1.879673117656213</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6109925736265305</v>
+        <v>0.6146459062103785</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.08520702858686036</v>
+        <v>0.08263851055910054</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1620566205950595</v>
+        <v>0.1553333867810904</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1.901916112822293</v>
+        <v>1.879673117656213</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.6109925736265305</v>
+        <v>0.6146459062103785</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.08520702858686036</v>
+        <v>0.08263851055910054</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1620566205950595</v>
+        <v>0.1553333867810904</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1325518323395183</v>
+        <v>0.1323113440314841</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1225619813220132</v>
+        <v>0.123361321436888</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,23 +1276,23 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1213798401081743</v>
+        <v>0.1204761636237952</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.09430858433978111</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BK3" t="n">
-        <v>0.09514317330296665</v>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="BM3" t="n">
-        <v>0.09418819041667802</v>
+        <v>0.09414090939653268</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.06974403847594821</v>
+        <v>0.07081586022642214</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.05413806733721188</v>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BQ3" t="n">
-        <v>0.05360248570813517</v>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
       <c r="BS3" t="n">
-        <v>0.05359789965488153</v>
+        <v>0.05264448061537663</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04239987344116766</v>
+        <v>0.04186495817808867</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03619154618045903</v>
+        <v>0.0360490183494178</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-12.xlsx
+++ b/outputs/daily/predictions_2026-06-12.xlsx
@@ -843,31 +843,31 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.490283585198356</v>
+        <v>1.492884648315965</v>
       </c>
       <c r="L2" t="n">
-        <v>1.092344046340702</v>
+        <v>1.095242983223093</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3560472142682399</v>
+        <v>0.3560106393859271</v>
       </c>
       <c r="O2" t="n">
-        <v>0.308401348237844</v>
+        <v>0.3081587611262273</v>
       </c>
       <c r="P2" t="n">
-        <v>0.335551437493916</v>
+        <v>0.3358305994878457</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4333415671715702</v>
+        <v>0.4353871555505382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.228211897706258</v>
+        <v>1.232941103374638</v>
       </c>
       <c r="S2" t="n">
-        <v>1.181788102293742</v>
+        <v>1.187058896625362</v>
       </c>
       <c r="T2" t="n">
         <v>0.6021160820980298</v>
@@ -885,58 +885,58 @@
         <v>0.5599628463344619</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4512131781781549</v>
+        <v>0.451224615408004</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2833206666038897</v>
+        <v>0.2829899943382564</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2654661552179555</v>
+        <v>0.2657853902537395</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4772002109359952</v>
+        <v>0.4785855752122075</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5227997890640048</v>
+        <v>0.5214144247877925</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5271399184012189</v>
+        <v>0.5282680585414024</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4728600815987811</v>
+        <v>0.4717319414585976</v>
       </c>
       <c r="AF2" t="n">
         <v>0.45028</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2827</v>
+        <v>0.28232</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.26702</v>
+        <v>0.2674</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.47714</v>
+        <v>0.47836</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.527205</v>
+        <v>0.5283099999999999</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.48947</v>
+        <v>1.492165</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.09705</v>
+        <v>1.099795</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.58652</v>
+        <v>2.59196</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.4659628089861452</v>
+        <v>0.4659510383406823</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2815328673791875</v>
+        <v>0.2813531644681324</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2525043236346675</v>
+        <v>0.2526957971911853</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.4659628089861452</v>
+        <v>0.4659510383406823</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2.80861627314016</v>
+        <v>2.808904817352853</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4659628089861452</v>
+        <v>0.4659510383406823</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1099155947179052</v>
+        <v>0.1099403989547552</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3087107279965873</v>
+        <v>0.3088121162457065</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2.80861627314016</v>
+        <v>2.808904817352853</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.4659628089861452</v>
+        <v>0.4659510383406823</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1099155947179052</v>
+        <v>0.1099403989547552</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.3087107279965873</v>
+        <v>0.3088121162457065</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.1353319549559535</v>
+        <v>0.1351823860425634</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.1003255753551344</v>
+        <v>0.09991691500063339</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>0.09167408682893671</v>
+        <v>0.09173259492984782</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0.0878781052261851</v>
+        <v>0.08744998614321814</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>0.08392418774656241</v>
+        <v>0.08375547374875317</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>0.07025121502645797</v>
+        <v>0.07002989772349485</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.06719502512535629</v>
+        <v>0.06729889080385131</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.05006982147565478</v>
+        <v>0.05023474046488104</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.04554012892973772</v>
+        <v>0.04564872757365224</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.04508875075371153</v>
+        <v>0.04507976612912942</v>
       </c>
     </row>
     <row r="3">
@@ -1114,31 +1114,31 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.722157141352893</v>
+        <v>1.711170788624602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7644907110372486</v>
+        <v>0.7644770637655399</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.532007395651278</v>
+        <v>0.5253076359157678</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2648563657036375</v>
+        <v>0.2696169093227022</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2031362386450845</v>
+        <v>0.2050754547615301</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4460436550382903</v>
+        <v>0.4414751901811675</v>
       </c>
       <c r="R3" t="n">
-        <v>1.587661384469602</v>
+        <v>1.56768619769089</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8723386155303982</v>
+        <v>0.8723138023091096</v>
       </c>
       <c r="T3" t="n">
         <v>0.7255353306240498</v>
@@ -1156,58 +1156,58 @@
         <v>0.4133217268355135</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5916223289257996</v>
+        <v>0.5889922449275227</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2563971966150133</v>
+        <v>0.2578046505407257</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1519804744591876</v>
+        <v>0.153203104531752</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4527561768691967</v>
+        <v>0.4499240726842711</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5472438231308032</v>
+        <v>0.550075927315729</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4498892667997818</v>
+        <v>0.4488794790700054</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5501107332002182</v>
+        <v>0.5511205209299946</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.59251</v>
+        <v>0.589665</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.25501</v>
+        <v>0.256725</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.15248</v>
+        <v>0.15361</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.452445</v>
+        <v>0.449835</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.44887</v>
+        <v>0.448005</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.722655</v>
+        <v>1.711885</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.76415</v>
+        <v>0.764175</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.486805</v>
+        <v>2.47606</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6146459062103785</v>
+        <v>0.6113084813166052</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2377947455113866</v>
+        <v>0.2400508264404406</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.147559348278235</v>
+        <v>0.1486406922429543</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.6146459062103785</v>
+        <v>0.6113084813166052</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.879673117656213</v>
+        <v>1.903646419029684</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6146459062103785</v>
+        <v>0.6113084813166052</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.08263851055910054</v>
+        <v>0.08600084540083752</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1553333867810904</v>
+        <v>0.1637152013808296</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1.879673117656213</v>
+        <v>1.903646419029684</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.6146459062103785</v>
+        <v>0.6113084813166052</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.08263851055910054</v>
+        <v>0.08600084540083752</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1553333867810904</v>
+        <v>0.1637152013808296</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1323113440314841</v>
+        <v>0.1329215786291662</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.123361321436888</v>
+        <v>0.1231394930739216</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,23 +1276,23 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1204761636237952</v>
+        <v>0.1210294736176899</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.09511132538647291</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BK3" t="n">
-        <v>0.09430858433978111</v>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
       <c r="BM3" t="n">
-        <v>0.09414090939653268</v>
+        <v>0.09413731809872859</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.07081586022642214</v>
+        <v>0.07023756782471201</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.05413806733721188</v>
+        <v>0.05369500961666879</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.05264448061537663</v>
+        <v>0.05329645128611508</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04186495817808867</v>
+        <v>0.04205648028197295</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.0360490183494178</v>
+        <v>0.03598291026543933</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-12.xlsx
+++ b/outputs/daily/predictions_2026-06-12.xlsx
@@ -1114,31 +1114,31 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.711170788624602</v>
+        <v>1.686355034841167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7644770637655399</v>
+        <v>0.7452928175489748</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5253076359157678</v>
+        <v>0.5247826970818131</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2696169093227022</v>
+        <v>0.2744765168529203</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2050754547615301</v>
+        <v>0.2007407860652665</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4414751901811675</v>
+        <v>0.4210441140527445</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56768619769089</v>
+        <v>1.522566645357372</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8723138023091096</v>
+        <v>0.8374333546426276</v>
       </c>
       <c r="T3" t="n">
         <v>0.7255353306240498</v>
@@ -1156,58 +1156,58 @@
         <v>0.4133217268355135</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5889922449275227</v>
+        <v>0.5880923770682798</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2578046505407257</v>
+        <v>0.2604067884092162</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.153203104531752</v>
+        <v>0.1515008345225044</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4499240726842711</v>
+        <v>0.438536623309367</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.550075927315729</v>
+        <v>0.561463376690633</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4488794790700054</v>
+        <v>0.4391496063973743</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5511205209299946</v>
+        <v>0.5608503936026257</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.589665</v>
+        <v>0.5891</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.256725</v>
+        <v>0.258995</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.15361</v>
+        <v>0.151905</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.449835</v>
+        <v>0.438195</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.448005</v>
+        <v>0.438025</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.711885</v>
+        <v>1.68728</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.764175</v>
+        <v>0.74422</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.47606</v>
+        <v>2.4315</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6113084813166052</v>
+        <v>0.6108735388182126</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2400508264404406</v>
+        <v>0.2426452039196505</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1486406922429543</v>
+        <v>0.1464812572621369</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.6113084813166052</v>
+        <v>0.6108735388182126</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.903646419029684</v>
+        <v>1.905550631834382</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6113084813166052</v>
+        <v>0.6108735388182126</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.08600084540083752</v>
+        <v>0.08609084173639936</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1637152013808296</v>
+        <v>0.1640504578659496</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1.903646419029684</v>
+        <v>1.905550631834382</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.6113084813166052</v>
+        <v>0.6108735388182126</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.08600084540083752</v>
+        <v>0.08609084173639936</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1637152013808296</v>
+        <v>0.1640504578659496</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1329215786291662</v>
+        <v>0.1371706465744768</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1231394930739216</v>
+        <v>0.1249733816116398</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1210294736176899</v>
+        <v>0.1215117077402489</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.09511132538647291</v>
+        <v>0.0989385477866831</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.09413731809872859</v>
+        <v>0.09314176369996227</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.07023756782471201</v>
+        <v>0.07024983043397176</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.05445877897439853</v>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BQ3" t="n">
-        <v>0.05369500961666879</v>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="BS3" t="n">
-        <v>0.05329645128611508</v>
+        <v>0.05235669405647253</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04205648028197295</v>
+        <v>0.0411644559213262</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03598291026543933</v>
+        <v>0.03470894374971285</v>
       </c>
     </row>
   </sheetData>
